--- a/public/assets/format_excel/mapel.xlsx
+++ b/public/assets/format_excel/mapel.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikko\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\ujian\public\assets\format_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEA2818-252F-4E17-854E-2B0A7C6F7D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0306DAD6-BE13-4966-83A1-76A4D9B6C96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10FE4C57-2589-4B61-99CD-ECEA947F5EB7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{10FE4C57-2589-4B61-99CD-ECEA947F5EB7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Mapel" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>no</t>
   </si>
@@ -119,13 +117,40 @@
     <t>TES MAPEL LPK3</t>
   </si>
   <si>
-    <t>04/13/2026</t>
-  </si>
-  <si>
-    <t>04/14/2026</t>
-  </si>
-  <si>
-    <t>04/15/2026</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>20/04/2027</t>
+  </si>
+  <si>
+    <t>20/04/2028</t>
+  </si>
+  <si>
+    <t>20/04/2029</t>
+  </si>
+  <si>
+    <t>20/04/2030</t>
+  </si>
+  <si>
+    <t>20/04/2031</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>01:00</t>
   </si>
 </sst>
 </file>
@@ -142,14 +167,17 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -168,45 +196,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,226 +537,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D44184-F300-4D19-B0BE-6AB26411A8C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B40D24-010F-493D-8F67-7AC6EE26B7FB}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="69.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="3">
-        <v>46299</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G2" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H2" s="5">
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1">
         <v>10</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
-        <v>46330</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G3" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1">
         <v>10</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="3">
-        <v>46360</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="1">
         <v>10</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G5" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H5" s="5">
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="1">
         <v>10</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G6" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
         <v>10</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.3125</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="G7" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1">
         <v>10</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/assets/format_excel/mapel.xlsx
+++ b/public/assets/format_excel/mapel.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\ujian\public\assets\format_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikko\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0306DAD6-BE13-4966-83A1-76A4D9B6C96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0D5437-45AD-47DD-9C74-90506C1BB19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{10FE4C57-2589-4B61-99CD-ECEA947F5EB7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{10FE4C57-2589-4B61-99CD-ECEA947F5EB7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mapel" sheetId="3" r:id="rId1"/>
+    <sheet name="mapel" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="171">
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>tanggal</t>
-  </si>
-  <si>
     <t>durasi</t>
   </si>
   <si>
@@ -81,69 +78,9 @@
     <t>Teknik Komputer dan Jaringan</t>
   </si>
   <si>
-    <t>TEST01</t>
-  </si>
-  <si>
-    <t>TEST02</t>
-  </si>
-  <si>
-    <t>TEST03</t>
-  </si>
-  <si>
-    <t>TEST04</t>
-  </si>
-  <si>
-    <t>TEST05</t>
-  </si>
-  <si>
-    <t>TEST06</t>
-  </si>
-  <si>
-    <t>TES MAPEL TKR</t>
-  </si>
-  <si>
-    <t>TES MAPEL LAS</t>
-  </si>
-  <si>
-    <t>TES MAPEL TEI</t>
-  </si>
-  <si>
-    <t>TES MAPEL TKJ</t>
-  </si>
-  <si>
-    <t>TES MAPEL TSM</t>
-  </si>
-  <si>
-    <t>TES MAPEL LPK3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20/04/2026</t>
   </si>
   <si>
-    <t>20/04/2027</t>
-  </si>
-  <si>
-    <t>20/04/2028</t>
-  </si>
-  <si>
-    <t>20/04/2029</t>
-  </si>
-  <si>
-    <t>20/04/2030</t>
-  </si>
-  <si>
-    <t>20/04/2031</t>
-  </si>
-  <si>
     <t>07:30</t>
   </si>
   <si>
@@ -151,13 +88,472 @@
   </si>
   <si>
     <t>01:00</t>
+  </si>
+  <si>
+    <t>TKR01</t>
+  </si>
+  <si>
+    <t>DASAR-DASAR KEJURUAN TKR KELAS 10</t>
+  </si>
+  <si>
+    <t>TKR02</t>
+  </si>
+  <si>
+    <t>SISTEM CHASIS KELAS 11</t>
+  </si>
+  <si>
+    <t>TKR03</t>
+  </si>
+  <si>
+    <t>SISTEM CHASIS KELAS 12</t>
+  </si>
+  <si>
+    <t>TKR04</t>
+  </si>
+  <si>
+    <t>SISTEM PEMINDAH TENAGA KELAS 11</t>
+  </si>
+  <si>
+    <t>TKR05</t>
+  </si>
+  <si>
+    <t>SISTEM PEMINDAH TENAGA KELAS 12</t>
+  </si>
+  <si>
+    <t>TKR06</t>
+  </si>
+  <si>
+    <t>SISTEM ENGINE KELAS 11</t>
+  </si>
+  <si>
+    <t>TKR07</t>
+  </si>
+  <si>
+    <t>SISTEM ENGINE KELAS 12</t>
+  </si>
+  <si>
+    <t>TKR08</t>
+  </si>
+  <si>
+    <t>SISTEM KELISTRIKAN OTOMOTIF KELAS 11</t>
+  </si>
+  <si>
+    <t>TKR09</t>
+  </si>
+  <si>
+    <t>SISTEM KELISTRIKAN OTOMOTIF KELAS 12</t>
+  </si>
+  <si>
+    <t>TEI01</t>
+  </si>
+  <si>
+    <t>DASAR-DASAR KEJURUAN TEI KELAS 10</t>
+  </si>
+  <si>
+    <t>TEI02</t>
+  </si>
+  <si>
+    <t>PENERAPAN RANGKAIAN ELEKTRONIKA KELAS 11</t>
+  </si>
+  <si>
+    <t>TEI03</t>
+  </si>
+  <si>
+    <t>SISTEM KENDALI ELEKTRONIK KELAS 11</t>
+  </si>
+  <si>
+    <t>TEI04</t>
+  </si>
+  <si>
+    <t>PEMELIHARAAN &amp; PERBAIKAN PERALATAN ELEKTRONIK INDUSTRI (PPPEI) KELAS 12</t>
+  </si>
+  <si>
+    <t>TEI05</t>
+  </si>
+  <si>
+    <t>PEMROGRAMAN SYSTEM EMBEDDED KELAS 11</t>
+  </si>
+  <si>
+    <t>TEI06</t>
+  </si>
+  <si>
+    <t>ANTARMUKA &amp; KOMUNKASI DATA KELAS 11</t>
+  </si>
+  <si>
+    <t>TEI07</t>
+  </si>
+  <si>
+    <t>SISTEM KENDALI INDUSTRI KELAS 12</t>
+  </si>
+  <si>
+    <t>TPL01</t>
+  </si>
+  <si>
+    <t>DASAR-DASAR KEJURUAN (DDK) TPL KELAS 10</t>
+  </si>
+  <si>
+    <t>TPL02</t>
+  </si>
+  <si>
+    <t>MUTU PENGELASAN KELAS 11</t>
+  </si>
+  <si>
+    <t>TPL03</t>
+  </si>
+  <si>
+    <t>GAMBAR TEKNIK KELAS 11</t>
+  </si>
+  <si>
+    <t>TPL04</t>
+  </si>
+  <si>
+    <t>LAS FCAW KELAS 12</t>
+  </si>
+  <si>
+    <t>TPL05</t>
+  </si>
+  <si>
+    <t>LAS BUSUR MANUAL KELAS 11</t>
+  </si>
+  <si>
+    <t>TPL06</t>
+  </si>
+  <si>
+    <t>LAS BUSUR MANUAL KELAS 12</t>
+  </si>
+  <si>
+    <t>TKJ01</t>
+  </si>
+  <si>
+    <t>DASAR-DASAR KEJURUAN TKJ KELAS 10</t>
+  </si>
+  <si>
+    <t>TKJ02</t>
+  </si>
+  <si>
+    <t>PERENCANAAN  &amp; PENGALAMATAN JARINGAN KELAS 11</t>
+  </si>
+  <si>
+    <t>TKJ03</t>
+  </si>
+  <si>
+    <t>PERENCANAAN  &amp; PENGALAMATAN JARINGAN KELAS 12</t>
+  </si>
+  <si>
+    <t>TKJ04</t>
+  </si>
+  <si>
+    <t>TEKNOLOGI JARINGAN KABEL &amp; NIRKABEL KELAS 11</t>
+  </si>
+  <si>
+    <t>TKJ05</t>
+  </si>
+  <si>
+    <t>TEKNOLOGI JARINGAN KABEL &amp; NIRKABEL KELAS 12</t>
+  </si>
+  <si>
+    <t>TKJ06</t>
+  </si>
+  <si>
+    <t>ADMINITRASI SISTEM JARINGAN KELAS 11</t>
+  </si>
+  <si>
+    <t>TKJ07</t>
+  </si>
+  <si>
+    <t>ADMINITRASI SISTEM JARINGAN KELAS 12</t>
+  </si>
+  <si>
+    <t>TKJ08</t>
+  </si>
+  <si>
+    <t>KEAMANAN JARINGAN KELAS 11</t>
+  </si>
+  <si>
+    <t>TKJ09</t>
+  </si>
+  <si>
+    <t>KEAMANAN JARINGAN KELAS 12</t>
+  </si>
+  <si>
+    <t>TKJ10</t>
+  </si>
+  <si>
+    <t>KONFIGURASI PERANGKAT JARINGAN KELAS 11</t>
+  </si>
+  <si>
+    <t>TKJ11</t>
+  </si>
+  <si>
+    <t>KONFIGURASI PERANGKAT JARINGAN KELAS 12</t>
+  </si>
+  <si>
+    <t>TSM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DASAR-DASAR KEJURUAN TSM KELAS 10 </t>
+  </si>
+  <si>
+    <t>TSM02</t>
+  </si>
+  <si>
+    <t>TSM03</t>
+  </si>
+  <si>
+    <t>SISTEM ENGINE KELAS  12</t>
+  </si>
+  <si>
+    <t>TSM04</t>
+  </si>
+  <si>
+    <t>TSM05</t>
+  </si>
+  <si>
+    <t>PENGOLOLAAN BENGKEL KELAS 12</t>
+  </si>
+  <si>
+    <t>TSM06</t>
+  </si>
+  <si>
+    <t>TSM07</t>
+  </si>
+  <si>
+    <t>FKK01</t>
+  </si>
+  <si>
+    <t>DASAR-DASAR KEJURUAN FKK KELAS 10</t>
+  </si>
+  <si>
+    <t>FKK02</t>
+  </si>
+  <si>
+    <t>FKK03</t>
+  </si>
+  <si>
+    <t>KEJURUAN FKK KELAS 12</t>
+  </si>
+  <si>
+    <t>PAI10</t>
+  </si>
+  <si>
+    <t>PAI &amp; Budi Pekerti Kelas 10</t>
+  </si>
+  <si>
+    <t>PAI11</t>
+  </si>
+  <si>
+    <t>PAI &amp; Budi Pekerti Kelas 11</t>
+  </si>
+  <si>
+    <t>PAI12</t>
+  </si>
+  <si>
+    <t>PAI &amp; Budi Pekerti Kelas 12</t>
+  </si>
+  <si>
+    <t>PKN10</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila Kelas 10</t>
+  </si>
+  <si>
+    <t>PKN11</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila Kelas 11</t>
+  </si>
+  <si>
+    <t>PKN12</t>
+  </si>
+  <si>
+    <t>Pendidikan Pancasila Kelas 12</t>
+  </si>
+  <si>
+    <t>MTK10</t>
+  </si>
+  <si>
+    <t>Matematika Kelas 10</t>
+  </si>
+  <si>
+    <t>MTK11</t>
+  </si>
+  <si>
+    <t>Matematika Kelas 11</t>
+  </si>
+  <si>
+    <t>MTK12</t>
+  </si>
+  <si>
+    <t>Matematika Kelas 12</t>
+  </si>
+  <si>
+    <t>SEJARAH10</t>
+  </si>
+  <si>
+    <t>Sejarah Indonesia Kelas 10</t>
+  </si>
+  <si>
+    <t>SEJARAH11</t>
+  </si>
+  <si>
+    <t>Sejarah Indonesia Kelas 11</t>
+  </si>
+  <si>
+    <t>IPAS10</t>
+  </si>
+  <si>
+    <t>PROJEK ILMU PENGETAHUAN ALAM &amp; SOSIAL Kelas 10</t>
+  </si>
+  <si>
+    <t>BING10</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris Kelas 10</t>
+  </si>
+  <si>
+    <t>BING11</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris Kelas 11</t>
+  </si>
+  <si>
+    <t>BING12</t>
+  </si>
+  <si>
+    <t>Bahasa Inggris Kelas 12</t>
+  </si>
+  <si>
+    <t>MTKPIL11</t>
+  </si>
+  <si>
+    <t>Matematika Pilihan Kelas 11</t>
+  </si>
+  <si>
+    <t>MTKPIL12</t>
+  </si>
+  <si>
+    <t>Matematika Pilihan Kelas 12</t>
+  </si>
+  <si>
+    <t>BI10</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia Kelas 10</t>
+  </si>
+  <si>
+    <t>BI11</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia Kelas 11</t>
+  </si>
+  <si>
+    <t>BI12</t>
+  </si>
+  <si>
+    <t>Bahasa Indonesia Kelas 12</t>
+  </si>
+  <si>
+    <t>PKK11</t>
+  </si>
+  <si>
+    <t>PROJEK ILMU &amp; KEWIRAUSAHAAN Kelas 11</t>
+  </si>
+  <si>
+    <t>PKK12</t>
+  </si>
+  <si>
+    <t>PROJEK ILMU &amp; KEWIRAUSAHAAN Kelas 12</t>
+  </si>
+  <si>
+    <t>KEMUH10</t>
+  </si>
+  <si>
+    <t>Kemuhammadiyahan Kelas 10</t>
+  </si>
+  <si>
+    <t>KEMUH11</t>
+  </si>
+  <si>
+    <t>Kemuhammadiyahan Kelas 11</t>
+  </si>
+  <si>
+    <t>KEMUH12</t>
+  </si>
+  <si>
+    <t>Kemuhammadiyahan Kelas 12</t>
+  </si>
+  <si>
+    <t>SENI10</t>
+  </si>
+  <si>
+    <t>Seni Budaya Kelas 10</t>
+  </si>
+  <si>
+    <t>BTQ10</t>
+  </si>
+  <si>
+    <t>Baca Tulis Quran Kelas 10</t>
+  </si>
+  <si>
+    <t>BTQ11</t>
+  </si>
+  <si>
+    <t>Baca Tulis Quran Kelas 11</t>
+  </si>
+  <si>
+    <t>BTQ12</t>
+  </si>
+  <si>
+    <t>Baca Tulis Quran Kelas 12</t>
+  </si>
+  <si>
+    <t>PJOK10</t>
+  </si>
+  <si>
+    <t>Pendidikan Jasmani Olahraga Kesehatan Kelas 10</t>
+  </si>
+  <si>
+    <t>PJOK11</t>
+  </si>
+  <si>
+    <t>Pendidikan Jasmani Olahraga Kesehatan Kelas 11</t>
+  </si>
+  <si>
+    <t>BA10</t>
+  </si>
+  <si>
+    <t>Bahasa Arab Kelas 10</t>
+  </si>
+  <si>
+    <t>BA11</t>
+  </si>
+  <si>
+    <t>Bahasa Arab Kelas 11</t>
+  </si>
+  <si>
+    <t>BA12</t>
+  </si>
+  <si>
+    <t>Bahasa Arab Kelas 12</t>
+  </si>
+  <si>
+    <t>TI10</t>
+  </si>
+  <si>
+    <t>Informatika Kelas 10</t>
+  </si>
+  <si>
+    <t>KEJURUAN FKK KELAS 11</t>
+  </si>
+  <si>
+    <t>tanggal ujian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,12 +565,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -202,8 +592,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,49 +927,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B40D24-010F-493D-8F67-7AC6EE26B7FB}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926CEC0E-334C-4849-B8B1-E91AFC8D4536}">
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="56.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -587,54 +965,54 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1">
         <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
@@ -642,123 +1020,2139 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H4" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="1">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="1">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="1">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="1">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="1">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="1">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="1">
+        <v>11</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1">
+        <v>12</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="1">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="1">
+        <v>12</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="1">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="1">
+        <v>12</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="1">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="1">
+        <v>12</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="1">
+        <v>11</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="1">
+        <v>12</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="1">
+        <v>11</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="1">
+        <v>12</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="1">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="1">
+        <v>11</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="1">
+        <v>12</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="1">
+        <v>11</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="H6" s="1">
+      <c r="B39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="1">
+        <v>12</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="1">
+        <v>11</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="1">
+        <v>12</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="1">
         <v>10</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="I42" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="1">
+        <v>11</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="1">
+        <v>12</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="1">
         <v>10</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="1">
+        <v>11</v>
+      </c>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="1">
+        <v>12</v>
+      </c>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="1">
         <v>10</v>
       </c>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="1">
+        <v>11</v>
+      </c>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="1">
+        <v>12</v>
+      </c>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="1">
+        <v>10</v>
+      </c>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="1">
+        <v>11</v>
+      </c>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="1">
+        <v>12</v>
+      </c>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="1">
+        <v>10</v>
+      </c>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="1">
+        <v>11</v>
+      </c>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="1">
+        <v>10</v>
+      </c>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="1">
+        <v>10</v>
+      </c>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="1">
+        <v>11</v>
+      </c>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="1">
+        <v>12</v>
+      </c>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="1">
+        <v>11</v>
+      </c>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" s="1">
+        <v>12</v>
+      </c>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="1">
+        <v>10</v>
+      </c>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" s="1">
+        <v>11</v>
+      </c>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" s="1">
+        <v>12</v>
+      </c>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65" s="1">
+        <v>11</v>
+      </c>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="1">
+        <v>12</v>
+      </c>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H67" s="1">
+        <v>10</v>
+      </c>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H68" s="1">
+        <v>11</v>
+      </c>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H69" s="1">
+        <v>12</v>
+      </c>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="1">
+        <v>10</v>
+      </c>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" s="1">
+        <v>10</v>
+      </c>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="1">
+        <v>11</v>
+      </c>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="1">
+        <v>12</v>
+      </c>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="1">
+        <v>10</v>
+      </c>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="1">
+        <v>11</v>
+      </c>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="1">
+        <v>10</v>
+      </c>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="1">
+        <v>11</v>
+      </c>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="1">
+        <v>12</v>
+      </c>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="1">
+        <v>10</v>
+      </c>
+      <c r="I79" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>